--- a/results/ai_run/all_images/quantification/quantification_all_images.xlsx
+++ b/results/ai_run/all_images/quantification/quantification_all_images.xlsx
@@ -640,7 +640,7 @@
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>17.2667</v>
+        <v>15.8</v>
       </c>
       <c r="H2" t="n">
         <v>514.4</v>
@@ -673,7 +673,7 @@
         <v>0.0432981</v>
       </c>
       <c r="R2" t="n">
-        <v>6.4008</v>
+        <v>5.7574</v>
       </c>
       <c r="S2" t="n">
         <v>477.8</v>
@@ -764,7 +764,7 @@
         <v>3684</v>
       </c>
       <c r="G3" t="n">
-        <v>16.1818</v>
+        <v>12.4545</v>
       </c>
       <c r="H3" t="n">
         <v>517.9091</v>
@@ -797,7 +797,7 @@
         <v>0.04193932</v>
       </c>
       <c r="R3" t="n">
-        <v>4.7828</v>
+        <v>3.5009</v>
       </c>
       <c r="S3" t="n">
         <v>481.5455</v>
@@ -888,7 +888,7 @@
         <v>2066</v>
       </c>
       <c r="G4" t="n">
-        <v>12.9167</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
         <v>410.1667</v>
@@ -921,7 +921,7 @@
         <v>0.04986605</v>
       </c>
       <c r="R4" t="n">
-        <v>5.8706</v>
+        <v>4.0113</v>
       </c>
       <c r="S4" t="n">
         <v>367.4167</v>
@@ -1012,7 +1012,7 @@
         <v>2188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14.25</v>
+        <v>8.166700000000001</v>
       </c>
       <c r="H5" t="n">
         <v>411.4167</v>
@@ -1045,7 +1045,7 @@
         <v>0.05005242</v>
       </c>
       <c r="R5" t="n">
-        <v>8.7387</v>
+        <v>4.0915</v>
       </c>
       <c r="S5" t="n">
         <v>384.9167</v>
@@ -1136,7 +1136,7 @@
         <v>1736</v>
       </c>
       <c r="G6" t="n">
-        <v>13.0909</v>
+        <v>9.545500000000001</v>
       </c>
       <c r="H6" t="n">
         <v>419.1818</v>
@@ -1169,7 +1169,7 @@
         <v>0.04904317</v>
       </c>
       <c r="R6" t="n">
-        <v>6.4973</v>
+        <v>4.6785</v>
       </c>
       <c r="S6" t="n">
         <v>391</v>
@@ -1260,7 +1260,7 @@
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>15.3333</v>
+        <v>13.6667</v>
       </c>
       <c r="H7" t="n">
         <v>492.7778</v>
@@ -1293,7 +1293,7 @@
         <v>0.0448407</v>
       </c>
       <c r="R7" t="n">
-        <v>6.3858</v>
+        <v>5.5684</v>
       </c>
       <c r="S7" t="n">
         <v>454.3333</v>
@@ -1384,7 +1384,7 @@
         <v>1519</v>
       </c>
       <c r="G8" t="n">
-        <v>14.0909</v>
+        <v>10.3636</v>
       </c>
       <c r="H8" t="n">
         <v>423.0909</v>
@@ -1417,7 +1417,7 @@
         <v>0.04428885</v>
       </c>
       <c r="R8" t="n">
-        <v>6.3641</v>
+        <v>4.6662</v>
       </c>
       <c r="S8" t="n">
         <v>389.8182</v>
@@ -1508,7 +1508,7 @@
         <v>1511.5</v>
       </c>
       <c r="G9" t="n">
-        <v>12.6154</v>
+        <v>8.2308</v>
       </c>
       <c r="H9" t="n">
         <v>343.6923</v>
@@ -1541,7 +1541,7 @@
         <v>0.04293153</v>
       </c>
       <c r="R9" t="n">
-        <v>7.1329</v>
+        <v>4.4574</v>
       </c>
       <c r="S9" t="n">
         <v>311.9231</v>
